--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1719,6 +1719,230 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/114749404</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135981423</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sandsjövägsåsen, Sandsjövägsåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>330249</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6420533</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135981423</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135982039</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sandsjövägsåsen, Vg</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>330289</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6420827</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ale</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Starrkärr</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Mats Eriksson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135982039</t>
         </is>
       </c>
     </row>
@@ -1733,6 +1957,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98138</v>
+        <v>98155</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98155</v>
+        <v>98156</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98156</v>
+        <v>98157</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 33802-2026 artfynd.xlsx
+++ b/artfynd/A 33802-2026 artfynd.xlsx
@@ -1727,7 +1727,7 @@
         <v>135981423</v>
       </c>
       <c r="B11" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>135982039</v>
       </c>
       <c r="B12" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
